--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>73</t>
+    <t>67</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,37 +57,37 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.164</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>0.534</t>
-  </si>
-  <si>
-    <t>(0.059)</t>
-  </si>
-  <si>
-    <t>0.288</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>(0.209)</t>
-  </si>
-  <si>
-    <t>1.425</t>
-  </si>
-  <si>
-    <t>(0.230)</t>
-  </si>
-  <si>
-    <t>0.466</t>
-  </si>
-  <si>
-    <t>(0.107)</t>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>0.582</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
+  </si>
+  <si>
+    <t>0.313</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>(0.227)</t>
+  </si>
+  <si>
+    <t>1.552</t>
+  </si>
+  <si>
+    <t>(0.245)</t>
+  </si>
+  <si>
+    <t>0.507</t>
+  </si>
+  <si>
+    <t>(0.115)</t>
   </si>
   <si>
     <t>43</t>
@@ -135,7 +135,7 @@
     <t>(0.300)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -147,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>0.349***</t>
-  </si>
-  <si>
-    <t>0.340***</t>
-  </si>
-  <si>
-    <t>0.373</t>
-  </si>
-  <si>
-    <t>2.668***</t>
-  </si>
-  <si>
-    <t>1.092***</t>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>0.302***</t>
+  </si>
+  <si>
+    <t>0.314***</t>
+  </si>
+  <si>
+    <t>0.325</t>
+  </si>
+  <si>
+    <t>2.541***</t>
+  </si>
+  <si>
+    <t>1.051***</t>
   </si>
 </sst>
 </file>
